--- a/CodeSystem-opd-sfk-antwort.xlsx
+++ b/CodeSystem-opd-sfk-antwort.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:42:42+00:00</t>
+    <t>2026-09-02T07:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
